--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N75_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N75_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>66.65552386070466</v>
+        <v>10.83152262736451</v>
       </c>
       <c r="D2" t="n">
-        <v>67.01697435872238</v>
+        <v>10.89025833329239</v>
       </c>
       <c r="E2" t="n">
-        <v>15.15645327650835</v>
+        <v>2.462923657432607</v>
       </c>
       <c r="F2" t="n">
-        <v>16.10761381951777</v>
+        <v>2.617487245671637</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.81083810939182</v>
+        <v>9.556761192776172</v>
       </c>
       <c r="D3" t="n">
-        <v>59.4481826354365</v>
+        <v>9.660329678258432</v>
       </c>
       <c r="E3" t="n">
-        <v>15.15645327650835</v>
+        <v>2.462923657432607</v>
       </c>
       <c r="F3" t="n">
-        <v>16.10761381951777</v>
+        <v>2.617487245671637</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.56823649323669</v>
+        <v>9.679838430150962</v>
       </c>
       <c r="D4" t="n">
-        <v>60.44494695152823</v>
+        <v>9.822303879623338</v>
       </c>
       <c r="E4" t="n">
-        <v>15.15645327650835</v>
+        <v>2.462923657432607</v>
       </c>
       <c r="F4" t="n">
-        <v>16.10761381951777</v>
+        <v>2.617487245671637</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.08233069264531</v>
+        <v>7.975878737554862</v>
       </c>
       <c r="D5" t="n">
-        <v>49.52187802578031</v>
+        <v>8.047305179189301</v>
       </c>
       <c r="E5" t="n">
-        <v>15.15645327650835</v>
+        <v>2.462923657432607</v>
       </c>
       <c r="F5" t="n">
-        <v>16.10761381951777</v>
+        <v>2.617487245671637</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.18994596914809</v>
+        <v>7.668366219986565</v>
       </c>
       <c r="D6" t="n">
-        <v>47.89017619163614</v>
+        <v>7.782153631140874</v>
       </c>
       <c r="E6" t="n">
-        <v>15.15645327650835</v>
+        <v>2.462923657432607</v>
       </c>
       <c r="F6" t="n">
-        <v>16.10761381951777</v>
+        <v>2.617487245671637</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>57.37203410129064</v>
+        <v>9.322955541459731</v>
       </c>
       <c r="D7" t="n">
-        <v>58.78835080105706</v>
+        <v>9.553107005171771</v>
       </c>
       <c r="E7" t="n">
-        <v>15.15645327650835</v>
+        <v>2.462923657432607</v>
       </c>
       <c r="F7" t="n">
-        <v>16.10761381951777</v>
+        <v>2.617487245671637</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>55.34382454735228</v>
+        <v>8.993371488944746</v>
       </c>
       <c r="D8" t="n">
-        <v>56.93401517031463</v>
+        <v>9.251777465176128</v>
       </c>
       <c r="E8" t="n">
-        <v>15.15645327650835</v>
+        <v>2.462923657432607</v>
       </c>
       <c r="F8" t="n">
-        <v>16.10761381951777</v>
+        <v>2.617487245671637</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.40262558546087</v>
+        <v>5.752926657637392</v>
       </c>
       <c r="D9" t="n">
-        <v>34.33504355737698</v>
+        <v>5.579444578073759</v>
       </c>
       <c r="E9" t="n">
-        <v>15.15645327650835</v>
+        <v>2.462923657432607</v>
       </c>
       <c r="F9" t="n">
-        <v>16.10761381951777</v>
+        <v>2.617487245671637</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.48395820379548</v>
+        <v>3.653643208116765</v>
       </c>
       <c r="D10" t="n">
-        <v>21.50091274439685</v>
+        <v>3.493898320964488</v>
       </c>
       <c r="E10" t="n">
-        <v>15.15645327650835</v>
+        <v>2.462923657432607</v>
       </c>
       <c r="F10" t="n">
-        <v>16.10761381951777</v>
+        <v>2.617487245671637</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>69.22914576656885</v>
+        <v>11.24973618706744</v>
       </c>
       <c r="D11" t="n">
-        <v>70.73085603901406</v>
+        <v>11.49376410633979</v>
       </c>
       <c r="E11" t="n">
-        <v>15.15645327650835</v>
+        <v>2.462923657432607</v>
       </c>
       <c r="F11" t="n">
-        <v>16.10761381951777</v>
+        <v>2.617487245671637</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>56.87704109532181</v>
+        <v>9.242519177989795</v>
       </c>
       <c r="D12" t="n">
-        <v>58.3143269439566</v>
+        <v>9.476078128392947</v>
       </c>
       <c r="E12" t="n">
-        <v>15.15645327650835</v>
+        <v>2.462923657432607</v>
       </c>
       <c r="F12" t="n">
-        <v>16.10761381951777</v>
+        <v>2.617487245671637</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.22721723891843</v>
+        <v>3.774422801324245</v>
       </c>
       <c r="D13" t="n">
-        <v>21.67138596853523</v>
+        <v>3.521600219886976</v>
       </c>
       <c r="E13" t="n">
-        <v>15.15645327650835</v>
+        <v>2.462923657432607</v>
       </c>
       <c r="F13" t="n">
-        <v>16.10761381951777</v>
+        <v>2.617487245671637</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.79388369791613</v>
+        <v>5.004006100911372</v>
       </c>
       <c r="D14" t="n">
-        <v>29.7432212975105</v>
+        <v>4.833273460845457</v>
       </c>
       <c r="E14" t="n">
-        <v>15.15645327650835</v>
+        <v>2.462923657432607</v>
       </c>
       <c r="F14" t="n">
-        <v>16.10761381951777</v>
+        <v>2.617487245671637</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
